--- a/owlcms/src/main/resources/templates/competitionBook/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F5797A-07B0-4A7A-8233-7B54181308B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC2D24C-B899-476D-88E0-C29CB4224A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="519" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="519" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -66,12 +66,6 @@
     <t>&lt;/jx:forEach&gt;</t>
   </si>
   <si>
-    <t>${l.snatchRank}</t>
-  </si>
-  <si>
-    <t>${l.cleanJerkRank}</t>
-  </si>
-  <si>
     <t>${nbClubs}</t>
   </si>
   <si>
@@ -369,9 +363,6 @@
     <t>${competition.womenPerTeamElseDefault}</t>
   </si>
   <si>
-    <t>${l.totalRank}</t>
-  </si>
-  <si>
     <t>&lt;jx:forEach items="${mTot}" groupBy="category.code"&gt;</t>
   </si>
   <si>
@@ -529,6 +520,15 @@
   </si>
   <si>
     <t>${l.bestLifterRank &lt; 0 ? t.get("Results.Extra/Invited") : l.bestLifterRank}</t>
+  </si>
+  <si>
+    <t>${l.snatchRank &lt; 0 ? 0 : l.snatchRank }</t>
+  </si>
+  <si>
+    <t>${l.cleanJerkRank &lt; 0 ? 0 : l.cleanJerkRank}</t>
+  </si>
+  <si>
+    <t>${l.totalRank &lt; 0 ? 0 : l.totalRank}</t>
   </si>
 </sst>
 </file>
@@ -1501,6 +1501,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1509,50 +1547,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1620,47 +1620,7 @@
     <cellStyle name="Titre 1 1 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Titre de la feuille" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2169,10 +2129,10 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="102" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C1" s="102"/>
       <c r="D1" s="102"/>
@@ -2182,18 +2142,18 @@
       <c r="H1" s="44"/>
       <c r="I1" s="44"/>
       <c r="J1" s="44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K1" s="45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" s="103"/>
       <c r="D2" s="103"/>
@@ -2203,18 +2163,18 @@
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
       <c r="J2" s="44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K2" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C3" s="103"/>
       <c r="D3" s="103"/>
@@ -2241,24 +2201,24 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="48"/>
       <c r="C8" s="48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J8" s="48"/>
       <c r="L8" s="49"/>
@@ -2283,42 +2243,42 @@
     </row>
     <row r="10" spans="1:19" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="I10" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="L10" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M10" s="45" t="s">
         <v>87</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="M10" s="45" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1"/>
       <c r="H11" s="44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I11" s="45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="1"/>
       <c r="M11" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N11" s="1"/>
       <c r="P11"/>
@@ -2328,22 +2288,22 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1"/>
       <c r="H12" s="44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J12" s="45"/>
       <c r="K12" s="1"/>
       <c r="M12" s="45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="45"/>
@@ -2353,15 +2313,15 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N13"/>
       <c r="S13"/>
@@ -2374,7 +2334,7 @@
       <c r="K14" s="45"/>
       <c r="L14" s="45"/>
       <c r="M14" s="45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N14" s="45"/>
       <c r="O14" s="45"/>
@@ -3865,10 +3825,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5522,58 +5482,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="113" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="115" t="s">
+      <c r="A1" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="117" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="107" t="s">
+      <c r="B1" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="107" t="s">
+      <c r="H1" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="I1" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="109" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="T1" s="105"/>
+      <c r="T1" s="115"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
       <c r="I2" s="34">
         <v>1</v>
       </c>
@@ -5584,10 +5544,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -5599,21 +5559,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="S2" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>64</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -5641,7 +5601,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -5668,7 +5628,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -5688,7 +5648,7 @@
     </row>
     <row r="7" spans="1:23" s="19" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>0</v>
@@ -5698,7 +5658,7 @@
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>2</v>
@@ -5707,43 +5667,43 @@
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="M7" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="O7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="N7" s="26" t="s">
+      <c r="P7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="Q7" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>39</v>
-      </c>
       <c r="R7" s="55" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S7" s="24" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -5802,11 +5762,11 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1"/>
-      <c r="R15" s="106"/>
+      <c r="R15" s="116"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="R16" s="106"/>
+      <c r="R16" s="116"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
@@ -6084,11 +6044,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="R15:R16"/>
     <mergeCell ref="F1:F2"/>
@@ -6096,22 +6051,19 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6166,58 +6118,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="113" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="115" t="s">
+      <c r="A1" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="117" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="107" t="s">
+      <c r="B1" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="107" t="s">
+      <c r="H1" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="I1" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="109" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="T1" s="105"/>
+      <c r="T1" s="115"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
       <c r="I2" s="34">
         <v>1</v>
       </c>
@@ -6228,10 +6180,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -6243,21 +6195,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="S2" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>64</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -6285,7 +6237,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -6312,7 +6264,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6330,7 +6282,7 @@
     </row>
     <row r="7" spans="1:23" s="19" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>0</v>
@@ -6340,7 +6292,7 @@
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>2</v>
@@ -6349,43 +6301,43 @@
         <v>3</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="M7" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="O7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="N7" s="26" t="s">
+      <c r="P7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="Q7" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>39</v>
-      </c>
       <c r="R7" s="55" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S7" s="24" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6445,11 +6397,11 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="P16" s="106"/>
+      <c r="P16" s="116"/>
     </row>
     <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
-      <c r="P17" s="106"/>
+      <c r="P17" s="116"/>
     </row>
     <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
@@ -6727,11 +6679,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="P16:P17"/>
     <mergeCell ref="F1:F2"/>
@@ -6739,22 +6686,19 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6807,46 +6751,46 @@
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="120" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="122" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>62</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S1" s="119"/>
       <c r="U1"/>
@@ -6857,7 +6801,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="107"/>
+      <c r="E2" s="112"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -6871,7 +6815,7 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="17">
         <v>1</v>
@@ -6883,19 +6827,19 @@
         <v>3</v>
       </c>
       <c r="P2" s="38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6917,7 +6861,7 @@
     </row>
     <row r="4" spans="1:22" s="19" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="37" t="s">
         <v>0</v>
@@ -6927,7 +6871,7 @@
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>2</v>
@@ -6936,43 +6880,43 @@
         <v>3</v>
       </c>
       <c r="H4" s="101" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I4" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="N4" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="25" t="s">
         <v>37</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="25" t="s">
-        <v>39</v>
       </c>
       <c r="Q4" s="24" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="V4" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -7306,7 +7250,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7353,46 +7297,46 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="120" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="122" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>62</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S1" s="119"/>
     </row>
@@ -7401,7 +7345,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="107"/>
+      <c r="E2" s="112"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -7415,7 +7359,7 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M2" s="17">
         <v>1</v>
@@ -7427,19 +7371,19 @@
         <v>3</v>
       </c>
       <c r="P2" s="38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7458,7 +7402,7 @@
     </row>
     <row r="4" spans="1:19" s="19" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="37" t="s">
         <v>0</v>
@@ -7468,7 +7412,7 @@
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>2</v>
@@ -7477,40 +7421,40 @@
         <v>3</v>
       </c>
       <c r="H4" s="101" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I4" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="L4" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="N4" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="O4" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="P4" s="25" t="s">
         <v>37</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="25" t="s">
-        <v>39</v>
       </c>
       <c r="Q4" s="24" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -7825,7 +7769,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7867,7 +7811,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7878,33 +7822,33 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="16"/>
       <c r="M4"/>
@@ -7917,28 +7861,28 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7965,7 +7909,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -7973,57 +7917,57 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -8044,43 +7988,43 @@
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8118,27 +8062,27 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -8184,7 +8128,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8195,33 +8139,33 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="16"/>
       <c r="M4"/>
@@ -8234,28 +8178,28 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8282,7 +8226,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8290,57 +8234,57 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -8361,43 +8305,43 @@
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8435,27 +8379,27 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -8501,7 +8445,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8512,36 +8456,36 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D3" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="68" t="s">
-        <v>53</v>
-      </c>
       <c r="M3" s="43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="16"/>
       <c r="M4"/>
@@ -8554,31 +8498,31 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="100" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8606,7 +8550,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8615,57 +8559,57 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -8686,43 +8630,43 @@
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M12" s="66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8760,35 +8704,35 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -8838,13 +8782,13 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:24" s="69" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J2" s="70"/>
     </row>
@@ -8874,54 +8818,54 @@
     </row>
     <row r="4" spans="1:24" s="82" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="73" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="76" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E4" s="77" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="78" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H4" s="79"/>
       <c r="I4" s="76" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J4" s="73" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K4" s="80"/>
       <c r="L4" s="74"/>
       <c r="M4" s="75"/>
       <c r="N4" s="73" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O4" s="74"/>
       <c r="P4" s="81"/>
       <c r="Q4" s="73" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R4" s="74"/>
       <c r="S4" s="73" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="T4" s="80"/>
       <c r="U4" s="73" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="V4" s="81"/>
       <c r="X4" s="75"/>
     </row>
     <row r="5" spans="1:24" s="87" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="83" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -8937,47 +8881,47 @@
     </row>
     <row r="6" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="88" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B6" s="89"/>
       <c r="C6" s="90"/>
       <c r="D6" s="91" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E6" s="92" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F6" s="88" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G6" s="92" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H6" s="90"/>
       <c r="I6" s="94" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J6" s="92" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K6" s="89"/>
       <c r="L6" s="89"/>
       <c r="M6" s="90"/>
       <c r="N6" s="92" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O6" s="89"/>
       <c r="P6" s="90"/>
       <c r="Q6" s="88" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R6" s="89"/>
       <c r="S6" s="93" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="T6" s="89"/>
       <c r="U6" s="95" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="V6" s="90"/>
       <c r="X6" s="90"/>
@@ -9004,7 +8948,7 @@
     </row>
     <row r="8" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="96" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
@@ -9023,10 +8967,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:D5">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/owlcms/src/main/resources/templates/competitionBook/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC2D24C-B899-476D-88E0-C29CB4224A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BADBD7-44D0-4EB5-9A1A-8D804D62C1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="519" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12105" tabRatio="519" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -180,9 +180,6 @@
     <t>${t.get("Lot")}</t>
   </si>
   <si>
-    <t>${t.get("Results.MenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Results.Teams")}</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
     <t>${t.get("Gender.M")}</t>
   </si>
   <si>
-    <t>${t.get("Results.WomenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Gender.F")}</t>
   </si>
   <si>
@@ -357,12 +351,6 @@
     <t>${group.weighInShortDateTime != "" ? (t.get("WeighInTime")+': '+group.weighInShortDateTime) : ""}</t>
   </si>
   <si>
-    <t>${competition.menPerTeamElseDefault}</t>
-  </si>
-  <si>
-    <t>${competition.womenPerTeamElseDefault}</t>
-  </si>
-  <si>
     <t>&lt;jx:forEach items="${mTot}" groupBy="category.code"&gt;</t>
   </si>
   <si>
@@ -529,6 +517,18 @@
   </si>
   <si>
     <t>${l.totalRank &lt; 0 ? 0 : l.totalRank}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.MenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.menBestNElseDefault}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.WomenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.womenBestNElseDefault}</t>
   </si>
 </sst>
 </file>
@@ -1501,6 +1501,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1530,29 +1553,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2129,10 +2129,10 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="102" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C1" s="102"/>
       <c r="D1" s="102"/>
@@ -2142,18 +2142,18 @@
       <c r="H1" s="44"/>
       <c r="I1" s="44"/>
       <c r="J1" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K1" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="103"/>
       <c r="D2" s="103"/>
@@ -2163,18 +2163,18 @@
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
       <c r="J2" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K2" s="45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C3" s="103"/>
       <c r="D3" s="103"/>
@@ -2201,24 +2201,24 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="48"/>
       <c r="C8" s="48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J8" s="48"/>
       <c r="L8" s="49"/>
@@ -2243,42 +2243,42 @@
     </row>
     <row r="10" spans="1:19" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="I10" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="L10" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="M10" s="45" t="s">
         <v>85</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="M10" s="45" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E11" s="1"/>
       <c r="H11" s="44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" s="45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="1"/>
       <c r="M11" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N11" s="1"/>
       <c r="P11"/>
@@ -2288,22 +2288,22 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" s="1"/>
       <c r="H12" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J12" s="45"/>
       <c r="K12" s="1"/>
       <c r="M12" s="45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="45"/>
@@ -2313,15 +2313,15 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N13"/>
       <c r="S13"/>
@@ -2334,7 +2334,7 @@
       <c r="K14" s="45"/>
       <c r="L14" s="45"/>
       <c r="M14" s="45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N14" s="45"/>
       <c r="O14" s="45"/>
@@ -3825,10 +3825,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5482,58 +5482,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="H1" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="I1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="112" t="s">
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="114" t="s">
-        <v>62</v>
-      </c>
-      <c r="T1" s="115"/>
+      <c r="T1" s="105"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="105"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="34">
         <v>1</v>
       </c>
@@ -5544,10 +5544,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -5559,21 +5559,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S2" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>62</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -5682,7 +5682,7 @@
         <v>33</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N7" s="26" t="s">
         <v>34</v>
@@ -5697,13 +5697,13 @@
         <v>37</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="S7" s="24" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -5762,11 +5762,11 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1"/>
-      <c r="R15" s="116"/>
+      <c r="R15" s="106"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="R16" s="116"/>
+      <c r="R16" s="106"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
@@ -6044,6 +6044,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="R15:R16"/>
     <mergeCell ref="F1:F2"/>
@@ -6051,11 +6056,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:C9">
     <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
@@ -6118,58 +6118,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="H1" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="I1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="112" t="s">
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="114" t="s">
-        <v>62</v>
-      </c>
-      <c r="T1" s="115"/>
+      <c r="T1" s="105"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="105"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="34">
         <v>1</v>
       </c>
@@ -6180,10 +6180,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N2" s="17">
         <v>1</v>
@@ -6195,21 +6195,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S2" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>62</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6316,7 +6316,7 @@
         <v>33</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N7" s="26" t="s">
         <v>34</v>
@@ -6331,13 +6331,13 @@
         <v>37</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="S7" s="24" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6397,11 +6397,11 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="P16" s="116"/>
+      <c r="P16" s="106"/>
     </row>
     <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
-      <c r="P17" s="116"/>
+      <c r="P17" s="106"/>
     </row>
     <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
@@ -6679,6 +6679,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="P16:P17"/>
     <mergeCell ref="F1:F2"/>
@@ -6686,11 +6691,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:C9">
     <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
@@ -6759,38 +6759,38 @@
       <c r="C1" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>58</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>60</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S1" s="119"/>
       <c r="U1"/>
@@ -6801,7 +6801,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="112"/>
+      <c r="E2" s="107"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -6831,15 +6831,15 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="32" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="28" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>2</v>
@@ -6910,10 +6910,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V4" s="21" t="s">
         <v>38</v>
@@ -7305,38 +7305,38 @@
       <c r="C1" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>58</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>60</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S1" s="119"/>
     </row>
@@ -7345,7 +7345,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="112"/>
+      <c r="E2" s="107"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -7375,15 +7375,15 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="32" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="28" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>2</v>
@@ -7451,10 +7451,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S4" s="35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -7811,7 +7811,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7822,28 +7822,28 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -7876,13 +7876,13 @@
         <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7909,7 +7909,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -7917,7 +7917,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>42</v>
@@ -7926,43 +7926,43 @@
         <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8000,31 +8000,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8062,7 +8062,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -8070,7 +8070,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8079,10 +8079,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -8128,7 +8128,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8139,28 +8139,28 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8193,13 +8193,13 @@
         <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8226,7 +8226,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8234,7 +8234,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>42</v>
@@ -8243,43 +8243,43 @@
         <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8317,31 +8317,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8379,7 +8379,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -8387,7 +8387,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8396,10 +8396,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8445,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8456,31 +8456,31 @@
     </row>
     <row r="3" spans="1:19" s="8" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="68" t="s">
-        <v>51</v>
-      </c>
       <c r="M3" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8516,13 +8516,13 @@
         <v>10</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8550,7 +8550,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8559,7 +8559,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>42</v>
@@ -8568,43 +8568,43 @@
         <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O10" s="68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8642,31 +8642,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>14</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8704,7 +8704,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
@@ -8712,7 +8712,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8721,18 +8721,18 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -8782,13 +8782,13 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:24" s="69" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J2" s="70"/>
     </row>
@@ -8818,54 +8818,54 @@
     </row>
     <row r="4" spans="1:24" s="82" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="73" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="76" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E4" s="77" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4" s="78" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H4" s="79"/>
       <c r="I4" s="76" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J4" s="73" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K4" s="80"/>
       <c r="L4" s="74"/>
       <c r="M4" s="75"/>
       <c r="N4" s="73" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O4" s="74"/>
       <c r="P4" s="81"/>
       <c r="Q4" s="73" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="R4" s="74"/>
       <c r="S4" s="73" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T4" s="80"/>
       <c r="U4" s="73" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="V4" s="81"/>
       <c r="X4" s="75"/>
     </row>
     <row r="5" spans="1:24" s="87" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="83" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -8881,47 +8881,47 @@
     </row>
     <row r="6" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="88" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B6" s="89"/>
       <c r="C6" s="90"/>
       <c r="D6" s="91" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E6" s="92" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F6" s="88" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G6" s="92" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H6" s="90"/>
       <c r="I6" s="94" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J6" s="92" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K6" s="89"/>
       <c r="L6" s="89"/>
       <c r="M6" s="90"/>
       <c r="N6" s="92" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O6" s="89"/>
       <c r="P6" s="90"/>
       <c r="Q6" s="88" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R6" s="89"/>
       <c r="S6" s="93" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="T6" s="89"/>
       <c r="U6" s="95" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="V6" s="90"/>
       <c r="X6" s="90"/>
@@ -8948,7 +8948,7 @@
     </row>
     <row r="8" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="96" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
